--- a/testakten/markenrechte-sicherungsuebertragung-insolvenz-mannheim/15_Forderungskonto_Rebenpfad.xlsx
+++ b/testakten/markenrechte-sicherungsuebertragung-insolvenz-mannheim/15_Forderungskonto_Rebenpfad.xlsx
@@ -2,9 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Saldo" sheetId="1" r:id="Rbe0b25885e4e479b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gegenrechnung_Schuldnerin" sheetId="2" r:id="Rb6ee8774b4b049ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sicherheiten" sheetId="3" r:id="R0abc487e709e4a77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Saldo" sheetId="1" r:id="R7222e90e71ab45f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gegenrechnung_Schuldnerin" sheetId="2" r:id="R75f8d3c654ce4167"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kontrollabgleich" sheetId="3" r:id="R2f50f51ba93b4afb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sicherheiten" sheetId="4" r:id="R90ac7824bbf2411d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -347,7 +348,7 @@
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
       <x:c r="A3" s="8" t="str">
-        <x:v>Arbeitsstand aus den beigefügten Aktenstücken; offene Angaben bleiben offen und sind nicht als Nullwert zu behandeln. Der Eingang vom 10.10.2025 wurde im Portfoliokauf-Verrechnungskonto erfasst. Ob er wirtschaftlich eine von der Schuldnerin geleistete Tilgung weiterleitete, ist in dieser Arbeitsmappe nicht entschieden. Die Zinsfortschreibung enthält keine Tagerechnung im Tabellenblatt; als Grundlage wird eine separate Systemauswertung genannt, die nicht in der Akte liegt.</x:v>
+        <x:v>Arbeitsstand aus den beigefügten Aktenstücken; offene Angaben bleiben offen und sind nicht als Nullwert zu behandeln. Der Eingang vom 10.10.2025 wurde im Portfoliokauf-Verrechnungskonto erfasst. Ob er wirtschaftlich eine von der Schuldnerin geleistete Tilgung weiterleitete, ist in dieser Arbeitsmappe nicht entschieden. Dieses Blatt bildet die unveränderte Parteibuchung von Rebenpfad ab. Die davon getrennte act/360-Nachrechnung und Kontrollsumme steht in 07A_Kreditkonto_und_Saldenstaffel.xlsx.</x:v>
       </x:c>
       <x:c r="B3" s="8"/>
       <x:c r="C3" s="8"/>
@@ -701,6 +702,153 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
+    <x:col min="1" max="1" width="42" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="13" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="39" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="24" customHeight="1">
+      <x:c r="A1" s="4" t="str">
+        <x:v>Forderungskonto und interne Saldenabstimmung der Rebenpfad Sicherheiten GmbH</x:v>
+      </x:c>
+      <x:c r="B1" s="4"/>
+      <x:c r="C1" s="4"/>
+      <x:c r="D1" s="4"/>
+      <x:c r="E1" s="4"/>
+    </x:row>
+    <x:row r="2" ht="24" customHeight="1">
+      <x:c r="A2" s="4"/>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+      <x:c r="D2" s="4"/>
+      <x:c r="E2" s="4"/>
+    </x:row>
+    <x:row r="3" ht="28" customHeight="1">
+      <x:c r="A3" s="8" t="str">
+        <x:v>Arbeitsstand aus den beigefügten Aktenstücken; offene Angaben bleiben offen und sind nicht als Nullwert zu behandeln. Die Kontrollwerte stammen aus Dokument 07A. Negative Differenzen bedeuten nicht automatisch ein Guthaben; sie markieren ungeklärte Parteibuchungen.</x:v>
+      </x:c>
+      <x:c r="B3" s="8"/>
+      <x:c r="C3" s="8"/>
+      <x:c r="D3" s="8"/>
+      <x:c r="E3" s="8"/>
+    </x:row>
+    <x:row r="5" ht="36" customHeight="1">
+      <x:c r="A5" s="11" t="str">
+        <x:v>Stichtag/Position</x:v>
+      </x:c>
+      <x:c r="B5" s="11" t="str">
+        <x:v>Rebenpfad EUR</x:v>
+      </x:c>
+      <x:c r="C5" s="11" t="str">
+        <x:v>neutrale Kontrolle EUR</x:v>
+      </x:c>
+      <x:c r="D5" s="11" t="str">
+        <x:v>Differenz EUR</x:v>
+      </x:c>
+      <x:c r="E5" s="11" t="str">
+        <x:v>Einordnung</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="34" customHeight="1">
+      <x:c r="A6" s="14" t="str">
+        <x:v>Kapital 31.07.2025 – Szenario Schuldnerweisung</x:v>
+      </x:c>
+      <x:c r="B6" s="14" t="n">
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="C6" s="14" t="n">
+        <x:v>192500</x:v>
+      </x:c>
+      <x:c r="D6" s="14" t="n">
+        <x:v>7500</x:v>
+      </x:c>
+      <x:c r="E6" s="14" t="str">
+        <x:v>Zuordnung Zahlung 31.03. streitig</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="34" customHeight="1">
+      <x:c r="A7" s="15" t="str">
+        <x:v>Kapital 31.07.2025 – Vertragskaskade</x:v>
+      </x:c>
+      <x:c r="B7" s="15" t="n">
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="C7" s="15" t="n">
+        <x:v>196100</x:v>
+      </x:c>
+      <x:c r="D7" s="15" t="n">
+        <x:v>3900</x:v>
+      </x:c>
+      <x:c r="E7" s="15" t="str">
+        <x:v>Q1-Zins 3.600; Rest Kapital</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="34" customHeight="1">
+      <x:c r="A8" s="14" t="str">
+        <x:v>Zinsen/Kosten 31.07.2025 bei Gläubigerzuordnung</x:v>
+      </x:c>
+      <x:c r="B8" s="14" t="n">
+        <x:v>6841.64</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="n">
+        <x:v>4840</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="n">
+        <x:v>2001.64</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="str">
+        <x:v>Kosten-/Rechenbeleg fehlt</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="34" customHeight="1">
+      <x:c r="A9" s="15" t="str">
+        <x:v>Zahlung 30.09./Eingang 10.10.2025</x:v>
+      </x:c>
+      <x:c r="B9" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="n">
+        <x:v>15000</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="n">
+        <x:v>-15000</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="str">
+        <x:v>keine Forderungsgutschrift trotz Geldeingang</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="34" customHeight="1">
+      <x:c r="A10" s="14" t="str">
+        <x:v>Zins 31.07.–31.12.2025 bei 200.000 Kapital</x:v>
+      </x:c>
+      <x:c r="B10" s="14" t="n">
+        <x:v>5968.36</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="n">
+        <x:v>6160</x:v>
+      </x:c>
+      <x:c r="D10" s="14" t="n">
+        <x:v>-191.64</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="str">
+        <x:v>act/360: 154 Tage</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:E2"/>
+    <x:mergeCell ref="A3:E3"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
     <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>

--- a/testakten/markenrechte-sicherungsuebertragung-insolvenz-mannheim/15_Forderungskonto_Rebenpfad.xlsx
+++ b/testakten/markenrechte-sicherungsuebertragung-insolvenz-mannheim/15_Forderungskonto_Rebenpfad.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Saldo" sheetId="1" r:id="R7222e90e71ab45f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gegenrechnung_Schuldnerin" sheetId="2" r:id="R75f8d3c654ce4167"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kontrollabgleich" sheetId="3" r:id="R2f50f51ba93b4afb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sicherheiten" sheetId="4" r:id="R90ac7824bbf2411d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Saldo" sheetId="1" r:id="R678082d30e2d4051"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gegenrechnung_Schuldnerin" sheetId="2" r:id="Rbffe85af753d476e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kontrollabgleich" sheetId="3" r:id="Rb8fab08944c94fa8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sicherheiten" sheetId="4" r:id="Ra6ac126ee771479f"/>
   </x:sheets>
 </x:workbook>
 </file>
